--- a/harga_pertanian_ternak.xlsx
+++ b/harga_pertanian_ternak.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,10 +16,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-  </numFmts>
-  <fonts count="1">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -27,13 +25,34 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00667eea"/>
+        <bgColor rgb="00667eea"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="0010b981"/>
+        <bgColor rgb="0010b981"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -54,19 +73,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -432,322 +445,1212 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Tanggal</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Jagung Pipil</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Jagung Pakan</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Kedelai Impor</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Kedelai Lokal</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Pakan Broiler</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Pakan Layer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Pakan Bebek</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Bungkil Kedelai</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Jagung Giling</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>46192.73992427083</v>
-      </c>
-      <c r="B2" t="n">
-        <v>6200</v>
-      </c>
-      <c r="C2" t="n">
-        <v>7000</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>8400</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>7800</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>13800</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>293100</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>272600</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>12400</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>7800</v>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>4400</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>8400</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>7800</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>14300</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>17500</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>274800</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>269500</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>12500</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>7700</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>4600</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>9500</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>8800</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>7700</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>13500</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>17600</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>292200</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>267500</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>12100</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>7700</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>4600</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>9100</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>8900</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>8200</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>13800</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>288900</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>266700</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>12600</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>7300</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>4400</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>9800</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>8400</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>7700</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>14100</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>18600</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>270900</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>266100</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>12200</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>7800</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>4400</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>9800</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>8900</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>7800</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>14000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>17500</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>292900</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>276700</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>7700</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>4400</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>9700</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>8400</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>7800</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>14100</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>18300</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>288900</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>267900</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>11900</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>7200</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>4700</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>8400</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>7600</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>14200</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>18700</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>293800</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>252200</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>12600</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>7400</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>4300</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>9400</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>8700</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>8300</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>14200</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>17400</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>266700</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>260200</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>11800</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>7800</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>4300</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>9500</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>8100</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>8300</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>14600</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>270300</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>272200</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>11800</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>7300</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>4600</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>9700</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>8500</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>7600</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>13400</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>18800</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>277200</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>275800</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>11900</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>7600</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>4600</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>9000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-07</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>8600</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>8300</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>14500</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>18400</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>278500</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>267100</v>
+      </c>
+      <c r="H13" s="3" t="n">
         <v>11500</v>
       </c>
-      <c r="E2" t="n">
-        <v>10200</v>
-      </c>
-      <c r="F2" t="n">
+      <c r="I13" s="3" t="n">
+        <v>7200</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>4600</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>9400</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
         <v>8300</v>
       </c>
-      <c r="G2" t="n">
+      <c r="C14" s="3" t="n">
         <v>7700</v>
       </c>
-      <c r="H2" t="n">
+      <c r="D14" s="3" t="n">
+        <v>14700</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>17400</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>275900</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>277700</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>12300</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>7500</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>4500</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>9400</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>8100</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>8100</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>13700</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>18300</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>284200</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>261200</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>7800</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>4300</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>9900</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>8300</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>7900</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>13600</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>18400</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>289500</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>277200</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>12100</v>
+      </c>
+      <c r="I16" s="3" t="n">
         <v>7100</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J16" s="3" t="n">
+        <v>4500</v>
+      </c>
+      <c r="K16" s="3" t="n">
         <v>9800</v>
       </c>
-      <c r="J2" t="n">
-        <v>6500</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>46193.73992427083</v>
-      </c>
-      <c r="B3" t="n">
-        <v>6250</v>
-      </c>
-      <c r="C3" t="n">
-        <v>7060</v>
-      </c>
-      <c r="D3" t="n">
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>8500</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>8400</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>13800</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>291200</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>252700</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>12400</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>7200</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>4400</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>9200</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>8900</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>7600</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>13600</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>18100</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>267200</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>256300</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>11500</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>7700</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>4700</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>9800</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>8200</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>8400</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>14100</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>17600</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>286100</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>271200</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>11900</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>7300</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>4400</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>9200</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-14</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>8400</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>8200</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>13600</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>17700</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>267900</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>272900</v>
+      </c>
+      <c r="H20" s="3" t="n">
         <v>11600</v>
       </c>
-      <c r="E3" t="n">
-        <v>10280</v>
-      </c>
-      <c r="F3" t="n">
-        <v>8370</v>
-      </c>
-      <c r="G3" t="n">
-        <v>7760</v>
-      </c>
-      <c r="H3" t="n">
-        <v>7150</v>
-      </c>
-      <c r="I3" t="n">
-        <v>9880</v>
-      </c>
-      <c r="J3" t="n">
-        <v>6550</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>46194.73992427083</v>
-      </c>
-      <c r="B4" t="n">
-        <v>6300</v>
-      </c>
-      <c r="C4" t="n">
-        <v>7120</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="I20" s="3" t="n">
+        <v>7400</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>4400</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>9100</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>8400</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>7600</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>14400</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>18200</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>291600</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>258200</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>12000</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>7600</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>4700</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>9400</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>8600</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>8000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>14100</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>285000</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>266000</v>
+      </c>
+      <c r="H22" s="3" t="n">
         <v>11700</v>
       </c>
-      <c r="E4" t="n">
-        <v>10360</v>
-      </c>
-      <c r="F4" t="n">
-        <v>8440</v>
-      </c>
-      <c r="G4" t="n">
-        <v>7820</v>
-      </c>
-      <c r="H4" t="n">
+      <c r="I22" s="3" t="n">
         <v>7200</v>
       </c>
-      <c r="I4" t="n">
-        <v>9960</v>
-      </c>
-      <c r="J4" t="n">
-        <v>6600</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>46195.73992427083</v>
-      </c>
-      <c r="B5" t="n">
-        <v>6350</v>
-      </c>
-      <c r="C5" t="n">
-        <v>7180</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="J22" s="3" t="n">
+        <v>4700</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>9100</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>8300</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>7900</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>13800</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>18200</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>293800</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>274000</v>
+      </c>
+      <c r="H23" s="3" t="n">
         <v>11800</v>
       </c>
-      <c r="E5" t="n">
-        <v>10440</v>
-      </c>
-      <c r="F5" t="n">
-        <v>8510</v>
-      </c>
-      <c r="G5" t="n">
-        <v>7880</v>
-      </c>
-      <c r="H5" t="n">
-        <v>7250</v>
-      </c>
-      <c r="I5" t="n">
-        <v>10040</v>
-      </c>
-      <c r="J5" t="n">
-        <v>6650</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>46196.73992427083</v>
-      </c>
-      <c r="B6" t="n">
-        <v>6400</v>
-      </c>
-      <c r="C6" t="n">
-        <v>7240</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="I23" s="3" t="n">
+        <v>7100</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>4400</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>8400</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>7700</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>13600</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>17700</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>293900</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>265700</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>12100</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>7600</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>4400</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>8100</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>8300</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>13600</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>18800</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>268100</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>252900</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>12400</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>7800</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>4400</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>9600</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>8900</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>8200</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>14200</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>18400</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>283700</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>271100</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>12100</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>7200</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>4700</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>9500</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>8100</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>7900</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>14200</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>17600</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>289000</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>263300</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>12500</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>7400</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>4300</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>9300</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>8100</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>8300</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>13700</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>17900</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>268500</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>254300</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>12200</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>7200</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>4600</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>9500</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>8300</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>7800</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>13800</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>18700</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>282100</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>273000</v>
+      </c>
+      <c r="H29" s="3" t="n">
         <v>11900</v>
       </c>
-      <c r="E6" t="n">
-        <v>10520</v>
-      </c>
-      <c r="F6" t="n">
-        <v>8580</v>
-      </c>
-      <c r="G6" t="n">
-        <v>7940</v>
-      </c>
-      <c r="H6" t="n">
-        <v>7300</v>
-      </c>
-      <c r="I6" t="n">
-        <v>10120</v>
-      </c>
-      <c r="J6" t="n">
-        <v>6700</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>46198.28889185185</v>
-      </c>
-      <c r="B7" t="n">
-        <v>6450</v>
-      </c>
-      <c r="C7" t="n">
-        <v>7300</v>
-      </c>
-      <c r="D7" t="n">
-        <v>12000</v>
-      </c>
-      <c r="E7" t="n">
-        <v>10600</v>
-      </c>
-      <c r="F7" t="n">
-        <v>8650</v>
-      </c>
-      <c r="G7" t="n">
-        <v>8000</v>
-      </c>
-      <c r="H7" t="n">
-        <v>7350</v>
-      </c>
-      <c r="I7" t="n">
-        <v>10200</v>
-      </c>
-      <c r="J7" t="n">
-        <v>6750</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>46198.28898179398</v>
-      </c>
-      <c r="B8" t="n">
-        <v>6500</v>
-      </c>
-      <c r="C8" t="n">
-        <v>7360</v>
-      </c>
-      <c r="D8" t="n">
-        <v>12100</v>
-      </c>
-      <c r="E8" t="n">
-        <v>10680</v>
-      </c>
-      <c r="F8" t="n">
-        <v>8720</v>
-      </c>
-      <c r="G8" t="n">
-        <v>8060</v>
-      </c>
-      <c r="H8" t="n">
-        <v>7400</v>
-      </c>
-      <c r="I8" t="n">
-        <v>10280</v>
-      </c>
-      <c r="J8" t="n">
-        <v>6800</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="I29" s="3" t="n">
+        <v>7600</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>4600</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>9700</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>8800</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>8100</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>14000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>17700</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>275000</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>257500</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>12400</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>7800</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>4500</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>9200</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="B9" s="4" t="n">
-        <v>6200</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>7000</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>11500</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>10200</v>
-      </c>
-      <c r="F9" s="4" t="n">
+      <c r="B31" s="3" t="n">
+        <v>8800</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>8300</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="D31" s="3" t="n">
+        <v>14500</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>285100</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>278200</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>12600</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>7200</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>4300</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>9200</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>8700</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>8200</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>14400</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>18500</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>274300</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>268900</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>11700</v>
+      </c>
+      <c r="I32" s="3" t="n">
         <v>7700</v>
       </c>
-      <c r="H9" s="4" t="n">
-        <v>7100</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>9800</v>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>6500</v>
-      </c>
-      <c r="K9" s="5" t="inlineStr">
-        <is>
-          <t>estimasi terakhir</t>
-        </is>
+      <c r="J32" s="3" t="n">
+        <v>4600</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>9300</v>
       </c>
     </row>
   </sheetData>
